--- a/file/table/DAPC_AreaExtent.xlsx
+++ b/file/table/DAPC_AreaExtent.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B28490BF-68A4-4EF5-AE51-61C07C092D54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD678014-F316-4071-A590-94EEDE6B9FF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{B2E63674-EE84-4EEF-9889-BCF292EE5960}"/>
   </bookViews>
@@ -315,10 +315,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -701,7 +701,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="11">
-        <v>4839065.9651104799</v>
+        <v>4439065.9651104799</v>
       </c>
       <c r="D5" s="12">
         <v>1970411.5557369899</v>
@@ -724,7 +724,7 @@
       </c>
       <c r="C7" s="7">
         <f>ABS(C6-C5)</f>
-        <v>51551.623698470183</v>
+        <v>451551.62369847018</v>
       </c>
       <c r="D7" s="6">
         <f>ABS(D6-D5)</f>
@@ -750,7 +750,7 @@
       </c>
       <c r="C11" s="13">
         <f>C7*D7</f>
-        <v>6296544302.6021051</v>
+        <v>55152769196.166092</v>
       </c>
     </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.6">
@@ -759,7 +759,7 @@
       </c>
       <c r="C12" s="13">
         <f>C11/10000</f>
-        <v>629654.43026021053</v>
+        <v>5515276.9196166089</v>
       </c>
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.6">
@@ -768,7 +768,7 @@
       </c>
       <c r="C13" s="14">
         <f>C11/1000000</f>
-        <v>6296.5443026021048</v>
+        <v>55152.769196166089</v>
       </c>
     </row>
   </sheetData>
